--- a/business_report_forms/008_resource_efficiency_measurement_report_form--business_report_forms.xlsx
+++ b/business_report_forms/008_resource_efficiency_measurement_report_form--business_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Resource Efficiency Measurement Report Form</t>
+          <t>Resource Efficiency Measurement</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Resource Efficiency Measurement Report</t>
+          <t>Resource Types</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Resource Efficiency Measurement Report</t>
+          <t>Report Type</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Resource Efficiency Measurement</t>
+          <t>Number of Resources</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Resource Measurement Report</t>
+          <t>Measurement Method</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Resource Measurement</t>
+          <t>Measurement Frequency</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Resource Use Measurement</t>
+          <t>Efficiency of Resource Use</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Resource Measurement Report</t>
+          <t>Resources Used</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Resource Efficiency Measurement</t>
+          <t>Measurement Report Format</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Resource Use Efficiency</t>
+          <t>Resources Measured</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Resource Measurement</t>
+          <t>Efficiency of Measurement</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Resource Use</t>
+          <t>Resource Being Measured</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Efficiency Measurement Report</t>
+          <t>Resource Use</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Use Efficiency</t>
+          <t>Resource Measurement</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Resource Use</t>
+          <t>Efficiency Report</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,7 +860,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Efficiency Measurement</t>
+          <t>Resource Use Efficiency</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,7 +883,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Resource Use Report</t>
+          <t>Use Report</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Measurement Efficiency</t>
+          <t>Efficiency Measurement</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Report Efficiency</t>
+          <t>Resource Efficiency</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Use Efficiency</t>
+          <t>Measurement Report</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Use Report</t>
+          <t>Efficiency</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Measurement Use</t>
+          <t>Use Efficiency</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Resource Measurement</t>
+          <t>Report Efficiency</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Use Measurement</t>
+          <t>Resource Efficiency Measurement Report Form Page 24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Resources</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>efficiency</t>
+          <t>resource_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Efficiency</t>
+          <t>Resource 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>measurement</t>
+          <t>resource_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Resource 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>resource_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Resource 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>resource_1</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Resource 1</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>resource_2</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Resource 2</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1216,19 +1216,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>resource_3</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Resource 3</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>resource_efficiency_measurement_report_form_page_10_choices</t>
+          <t>resource_efficiency_measurement_report_form_page_8_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>resource_efficiency_measurement_report_form_page_10_choices</t>
+          <t>resource_efficiency_measurement_report_form_page_8_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>resource_efficiency_measurement_report_form_page_10_choices</t>
+          <t>resource_efficiency_measurement_report_form_page_8_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,51 +1279,102 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>resource_efficiency_measurement_report_form_page_11_choices</t>
+          <t>resource_efficiency_measurement_report_form_page_9_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>efficiency</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Efficiency</t>
+          <t>PDF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>resource_efficiency_measurement_report_form_page_11_choices</t>
+          <t>resource_efficiency_measurement_report_form_page_9_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>measurement</t>
+          <t>excel</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Excel</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>resource_efficiency_measurement_report_form_page_11_choices</t>
+          <t>resource_efficiency_measurement_report_form_page_9_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>report</t>
+          <t>csv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>CSV</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>resource_efficiency_measurement_report_form_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>resource_1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Resource 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>resource_efficiency_measurement_report_form_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>resource_2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Resource 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>resource_efficiency_measurement_report_form_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>resource_3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Resource 3</t>
         </is>
       </c>
     </row>
